--- a/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
@@ -7,46 +7,46 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="40" state="visible" r:id="rId40"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
@@ -58,14 +58,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="53" state="visible" r:id="rId53"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.524</v>
+        <v>2.28</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -525,52 +550,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -599,6 +578,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>301710.cif</t>
         </is>
       </c>
@@ -607,7 +657,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -622,39 +672,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554324.cif</t>
+          <t>1617211.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.502</v>
+        <v>2.354</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1942974.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.331</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -667,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,47 +752,149 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.293</v>
+        <v>2.175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>301710.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.347</v>
+        <v>2.293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1940621.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>1617211.cif</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B8" t="n">
         <v>2.354</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -738,6 +902,951 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.293</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301697.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301710.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.012</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.495</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.499</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.519</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.539</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.509</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301182.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301182 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.844</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.366</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301531.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>527000.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.524</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -766,221 +1875,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>301489.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.175</v>
+        <v>2.314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.293</v>
+        <v>2.449</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.315</v>
+        <v>2.457</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1940621.cif</t>
+          <t>1942974.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.325</v>
+        <v>2.514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1955459.cif</t>
+          <t>301489.cif</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.328</v>
+        <v>2.546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>301697.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1617211.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+        <v>2.456</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+        <v>0.089</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301710.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.012</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301710.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.012</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1009,105 +2008,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300157.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.487</v>
+        <v>2.449</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300158.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.495</v>
+        <v>2.457</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>301489.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.499</v>
+        <v>2.546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>2.484</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.539</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>0.054</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1130,54 +2111,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301182.cif</t>
+          <t>301489.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.203</v>
+        <v>3.22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301182 2.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.203</v>
+        <v>3.242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300157.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1206,359 +2199,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.315</v>
+        <v>3.242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>529848.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+        <v>3.242</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301531.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.315</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>527000.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.151</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.151</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1587,245 +2270,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>1940621.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.314</v>
+        <v>2.325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301488.cif</t>
+          <t>1949113.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.449</v>
+        <v>2.431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+        <v>2.378</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1940621.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.325</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1949113.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
+        <v>0.075</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1838,7 +2335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1869,7 +2366,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -1884,9 +2381,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1894,98 +2418,6 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1949113.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.166</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301188.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2014,6 +2446,330 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>1949113.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.166</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.166</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301180.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301180 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301185.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>301185 2.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301183.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>301183 2.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>301184 2.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.443</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.443</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>301188.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>301182.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.447</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>301182 2.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.447</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>301181 2.cif</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>300163.cif</t>
         </is>
       </c>
@@ -2022,7 +2778,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2793,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2808,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -2067,9 +2823,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.529</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2082,7 +2865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2105,197 +2888,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301180.cif</t>
+          <t>301188.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.438</v>
+        <v>1.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301180 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.438</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301185.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>301185 2.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>301183.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.442</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>301183 2.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.442</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>301184 2.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.443</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>301184.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.443</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>301188.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>301182.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.447</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>301182 2.cif</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.447</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>301181.cif</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.455</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>301181 2.cif</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.455</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2308,7 +2936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2339,9 +2967,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2354,7 +3007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,9 +3038,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2400,7 +3078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,9 +3109,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2446,7 +3149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2477,9 +3180,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2492,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2523,9 +3251,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2538,7 +3291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2569,9 +3322,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2584,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2615,9 +3393,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.041</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2625,6 +3428,551 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.024</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.239</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.209</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.644</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.742</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2653,768 +4001,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>301180.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.024</v>
+        <v>1.197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>301180 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.207</v>
+        <v>1.197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.263</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>1.197</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.774</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300157.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.383</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.999</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301180.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301180 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.197</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301181.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301181 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301183.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301183 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301184 2.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301184.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>529848.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3443,6 +4089,427 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301181 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301183.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301183 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301184 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>301185.cif</t>
         </is>
       </c>
@@ -3451,7 +4518,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3466,7 +4533,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3481,7 +4548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -3496,9 +4563,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3511,7 +4605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3542,7 +4636,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3557,7 +4651,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3572,9 +4666,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3587,7 +4708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,7 +4739,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3633,9 +4754,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>deficiency</t>
-        </is>
-      </c>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3648,7 +4796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,9 +4827,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3694,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3725,9 +4898,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.141</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3740,7 +4938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,9 +4969,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.157</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3786,7 +5009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3817,9 +5040,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3832,7 +5080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,9 +5111,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.063</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3878,7 +5151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3909,9 +5182,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3924,7 +5222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3955,9 +5253,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.161</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3970,7 +5293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4001,9 +5324,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4016,7 +5364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4047,9 +5395,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4062,7 +5435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4085,32 +5458,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300171.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.179</v>
+        <v>2.537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4123,7 +5506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4146,17 +5529,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300171.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+      <c r="B3" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4169,7 +5594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4200,9 +5625,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4215,7 +5665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4246,9 +5696,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4261,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4292,9 +5767,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4307,7 +5807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4338,7 +5838,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -4353,9 +5853,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4368,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4399,9 +5926,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy_atomic_mixing</t>
-        </is>
-      </c>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
@@ -10,63 +10,64 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="52" state="visible" r:id="rId52"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -729,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,26 +753,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>301710.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.175</v>
+        <v>2.293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.293</v>
+        <v>2.347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -782,26 +783,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>554324.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.315</v>
+        <v>2.502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1940621.cif</t>
+          <t>1942974.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.325</v>
+        <v>2.514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -810,91 +811,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>2.414</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1617211.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.324</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>0.111</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -907,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -930,26 +871,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.293</v>
+        <v>2.175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>301710.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.347</v>
+        <v>2.293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -960,26 +901,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554324.cif</t>
+          <t>301531.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.502</v>
+        <v>2.315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
+          <t>1940621.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.514</v>
+        <v>2.325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -988,31 +929,91 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.414</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2.347</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1617211.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1852,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,104 +1876,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.314</v>
+        <v>3.242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301488.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>3.242</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1980,6 +1919,94 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.231</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2082,101 +2109,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.231</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,42 +2138,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>301488.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.457</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3433,7 +3434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3460,7 +3461,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.999</v>
+        <v>3.051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3469,29 +3470,76 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>1803318.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.999</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>3.239</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3499,377 +3547,6 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.207</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.239</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.263</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.209</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300157.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.383</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3972,7 +3649,220 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.241</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4060,7 +3950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4131,7 +4021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4228,94 +4118,6 @@
         <v>1.147</v>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301183.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301183 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4351,7 +4153,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301184 2.cif</t>
+          <t>301183.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4366,7 +4168,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301184.cif</t>
+          <t>301183 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4411,6 +4213,94 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301184 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4481,7 +4371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4599,7 +4489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4702,7 +4592,245 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4784,148 +4912,6 @@
         <v>0.051</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.241</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.241</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.141</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.141</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4961,11 +4947,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4985,7 +4971,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5032,15 +5018,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.063</v>
+        <v>3.157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5042,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.063</v>
+        <v>3.157</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5174,15 +5160,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>301531.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.125</v>
+        <v>3.063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5184,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.125</v>
+        <v>3.063</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5245,11 +5231,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.161</v>
+        <v>3.125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5269,7 +5255,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.161</v>
+        <v>3.125</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5316,15 +5302,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.146</v>
+        <v>3.161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5326,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.146</v>
+        <v>3.161</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5458,15 +5444,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300171.cif</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.537</v>
+        <v>3.146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5468,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.537</v>
+        <v>3.146</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5506,7 +5492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5529,11 +5515,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300171.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.179</v>
+        <v>2.537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5542,46 +5528,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.537</v>
+      </c>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.18</v>
-      </c>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5665,6 +5634,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
@@ -1,73 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sb-Sb" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="La-Sb" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Pt-Pt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Dy-Fe" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="In-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Er-Ge" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="Ho-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="Ni-Sb" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="Tb-Ge" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="Er-Ni" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="Gd-Si" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,7 +582,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.14</v>
+        <v>2.727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,7 +602,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.14</v>
+        <v>2.727</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -1853,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,42 +1875,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>301488.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.457</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1919,6 +1980,109 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.457</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2006,116 +2170,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.484</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2138,104 +2199,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.314</v>
+        <v>3.242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.449</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301488.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>3.242</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3434,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3461,7 +3460,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.051</v>
+        <v>2.644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3476,7 +3475,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.207</v>
+        <v>2.742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3491,7 +3490,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.239</v>
+        <v>2.774</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3500,46 +3499,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.72</v>
+      </c>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.203</v>
+        <v>0.068</v>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3552,7 +3536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3579,7 +3563,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.644</v>
+        <v>3.024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3594,7 +3578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.742</v>
+        <v>3.207</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3609,7 +3593,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.774</v>
+        <v>3.239</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3618,31 +3602,61 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Average</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="B8" t="n">
+        <v>3.209</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3655,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3678,11 +3692,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300169.cif</t>
+          <t>300163.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.241</v>
+        <v>2.233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3691,29 +3705,196 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>300170.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.241</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.28</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>300169.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>554324.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>300157.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300160.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>300161.cif</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.352</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>300162.cif</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.359</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.383</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.317</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B16" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3797,6 +3978,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301180.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301180 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.197</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3820,15 +4089,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1803318.cif</t>
+          <t>554324.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.975</v>
+        <v>2.302</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -3844,7 +4113,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.975</v>
+        <v>2.302</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3862,7 +4131,110 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301181.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301181 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300164.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.194</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3891,11 +4263,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301180.cif</t>
+          <t>301183.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.197</v>
+        <v>1.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3906,11 +4278,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301180 2.cif</t>
+          <t>301183 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.197</v>
+        <v>1.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3930,7 +4302,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.197</v>
+        <v>1.2</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -3944,180 +4316,6 @@
         <v>0</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301181.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301181 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.194</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1.869</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.147</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4153,7 +4351,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301183.cif</t>
+          <t>301184 2.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4168,7 +4366,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301183 2.cif</t>
+          <t>301184.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4213,6 +4411,298 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>529848.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301185.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301185 2.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>300158.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.135</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>300163.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.187</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4241,30 +4731,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301184 2.cif</t>
+          <t>1910757.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.2</v>
+        <v>2.886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301184.cif</t>
+          <t>1910757.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.2</v>
+        <v>2.958</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4770,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.2</v>
+        <v>2.922</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -4291,7 +4781,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -4300,7 +4790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4329,15 +4819,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>529848.cif</t>
+          <t>300169.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.531</v>
+        <v>3.241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4843,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.531</v>
+        <v>3.241</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -4365,465 +4855,6 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301185.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.199</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301185 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.199</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.187</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1.133</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.958</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.888</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300163.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300164.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300170.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300169.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>554324.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.302</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>300157.cif</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>300158.cif</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300160.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300161.cif</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300162.cif</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.359</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.383</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>300159.cif</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2.396</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.317</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4836,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4859,59 +4890,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1910757.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.886</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.958</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.141</v>
+      </c>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.922</v>
-      </c>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4947,11 +4961,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>3.157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4971,7 +4985,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.141</v>
+        <v>3.157</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5018,15 +5032,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>301531.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.157</v>
+        <v>3.063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5056,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.157</v>
+        <v>3.063</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5160,15 +5174,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.063</v>
+        <v>3.125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5198,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.063</v>
+        <v>3.125</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5231,11 +5245,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.125</v>
+        <v>3.161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5255,7 +5269,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.125</v>
+        <v>3.161</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5302,15 +5316,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.161</v>
+        <v>3.146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5340,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.161</v>
+        <v>3.146</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5444,15 +5458,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>300171.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.146</v>
+        <v>2.537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.146</v>
+        <v>2.537</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5492,7 +5506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5515,42 +5529,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>300171.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.537</v>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5634,6 +5665,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300170.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5657,30 +5759,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>529848.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.179</v>
+        <v>2.531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>300171.cif</t>
+          <t>300237.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.182</v>
+        <v>2.727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5798,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.18</v>
+        <v>2.629</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -5707,7 +5809,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002</v>
+        <v>0.139</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -5716,7 +5818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5745,15 +5847,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300170.cif</t>
+          <t>300237.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.227</v>
+        <v>3.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5871,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.227</v>
+        <v>3.14</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5781,165 +5883,6 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>529848.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.727</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.629</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
+++ b/20240307_histogram_test/output/20240307_histogram_test_site_pairs.xlsx
@@ -1,72 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rh-Si" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Rh-Rh" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sb-Sb" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="La-Sb" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="La-Pt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Pt-Pt" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Fe-Fe" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Si-Si" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Y-Si" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Y-Fe" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Ni-Si" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Ni-Ni" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Ga-Ga" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Ni-Ga" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Ce-Ga" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Ce-Ni" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Pd-Pd" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Ce-Pd" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Fe-Ga" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Dy-Fe" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Dy-Ga" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="In-In" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Lu-Ge" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="Fe-Ge" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="Gd-Ge" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="Er-Ge" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="Ho-Ge" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="Ni-Sb" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="Tb-Ge" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="Er-Ni" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="Ni-In" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="Sm-Ge" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="Nd-Ge" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="Gd-Si" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="Eu-Si" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="Pr-Ge" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="Ce-Si" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="Ir-Ge" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="Eu-Ge" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="Ce-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Rh" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ru-Ge" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ge-Ge" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Ge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Sb" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pt-Pt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sb-Sb" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Sb" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="La-Pt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Si" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Fe" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Fe" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Y-Si" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Ge" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ge" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Si" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ni" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Si" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ga" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ni" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Pd" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Pd" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-In" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ge" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yb-Ge" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ga" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Fe" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Dy" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pd-Si" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Si" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Pd" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lu-Ge" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fe-Ge" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ge" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ge" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ho-Ge" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Sb" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tb-Ge" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Ni" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-In" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sm-Ge" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nd-Ge" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Ni" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gd-Si" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Si" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pr-Ge" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Fe" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Si" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ir-Ge" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eu-Ge" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ce-Ge" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,11 +512,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.28</v>
+        <v>2.524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -531,7 +532,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.28</v>
+        <v>2.524</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -582,7 +583,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.727</v>
+        <v>3.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.727</v>
+        <v>3.14</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -729,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,26 +753,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.293</v>
+        <v>2.175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>301710.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.347</v>
+        <v>2.293</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -782,26 +783,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>554324.cif</t>
+          <t>301531.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.502</v>
+        <v>2.315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
+          <t>1940621.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.514</v>
+        <v>2.325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -810,31 +811,91 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1955459.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.328</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.414</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>2.347</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1617211.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>300808.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -847,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,26 +931,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>301710.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.175</v>
+        <v>2.293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301710.cif</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.293</v>
+        <v>2.347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,26 +961,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>554324.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.315</v>
+        <v>2.502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1940621.cif</t>
+          <t>1942974.cif</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.325</v>
+        <v>2.514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -928,91 +989,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1955459.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.328</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.347</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+        <v>2.414</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1617211.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>300808.cif</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2.324</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>0.111</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1418,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,11 +1472,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>529848.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.456</v>
+        <v>2.531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1484,31 +1485,46 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.366</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.444</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1521,7 +1537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,11 +1590,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>529848.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.531</v>
+        <v>2.456</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1587,46 +1603,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.366</v>
+      </c>
       <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.444</v>
+        <v>0.078</v>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1666,11 +1667,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.524</v>
+        <v>2.28</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1687,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.524</v>
+        <v>2.28</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -1852,7 +1853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1879,7 +1880,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.314</v>
+        <v>3.22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1894,7 +1895,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.449</v>
+        <v>3.242</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1903,76 +1904,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.457</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1942974.cif</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.514</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
+        <v>3.231</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>301489.cif</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.546</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.456</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>0.016</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1980,6 +1936,77 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301488.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3.242</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2082,101 +2109,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301489.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301488.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.231</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,42 +2138,104 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>301488.cif</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>301488.cif</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.242</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>2.457</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>1942974.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>301489.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2270,15 +2271,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1940621.cif</t>
+          <t>1949113.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.325</v>
+        <v>3.033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -2289,11 +2290,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.431</v>
+        <v>3.166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2310,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.378</v>
+        <v>3.1</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -2320,7 +2321,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.075</v>
+        <v>0.094</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -2358,15 +2359,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1949113.cif</t>
+          <t>1940621.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.033</v>
+        <v>2.325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deficiency without atomic mixing</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -2377,11 +2378,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.166</v>
+        <v>2.431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deficiency with atomic mixing</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2398,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.1</v>
+        <v>2.378</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -2408,7 +2409,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.094</v>
+        <v>0.075</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -3536,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3563,7 +3564,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.024</v>
+        <v>3.051</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3608,7 +3609,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.263</v>
+        <v>3.314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3617,46 +3618,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>1803318.cif</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3.314</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.203</v>
+      </c>
       <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Average</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.209</v>
+        <v>0.111</v>
       </c>
       <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3934,7 +3920,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.999</v>
+        <v>2.975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3954,7 +3940,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.999</v>
+        <v>2.975</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -3973,6 +3959,77 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1803318.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.999</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4060,7 +4117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4131,7 +4188,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4228,94 +4285,6 @@
         <v>1.147</v>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>301183.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>301183 2.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency without atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4351,7 +4320,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301184 2.cif</t>
+          <t>301183.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -4366,7 +4335,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>301184.cif</t>
+          <t>301183 2.cif</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -4411,6 +4380,94 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>301184 2.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>301184.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency without atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4481,7 +4538,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4599,7 +4656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4696,94 +4753,6 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2.886</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1910757.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.958</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Deficiency with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.922</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4867,7 +4836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4890,42 +4859,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300160.cif</t>
+          <t>1910757.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.141</v>
+        <v>2.886</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Deficiency with atomic mixing</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1910757.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.958</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deficiency with atomic mixing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.141</v>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.922</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4961,11 +4947,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300161.cif</t>
+          <t>300160.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4985,7 +4971,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.157</v>
+        <v>3.141</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5032,15 +5018,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301531.cif</t>
+          <t>300161.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.063</v>
+        <v>3.157</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5042,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.063</v>
+        <v>3.157</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5174,15 +5160,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300808.cif</t>
+          <t>301531.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.125</v>
+        <v>3.063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5184,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.125</v>
+        <v>3.063</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5245,11 +5231,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300162.cif</t>
+          <t>300808.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.161</v>
+        <v>3.125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5269,7 +5255,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.161</v>
+        <v>3.125</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5316,15 +5302,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>301697.cif</t>
+          <t>300162.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.146</v>
+        <v>3.161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5326,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.146</v>
+        <v>3.161</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5458,15 +5444,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300171.cif</t>
+          <t>301697.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.537</v>
+        <v>3.146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5468,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.537</v>
+        <v>3.146</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -5506,7 +5492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5529,11 +5515,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>300159.cif</t>
+          <t>300171.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.179</v>
+        <v>2.537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5542,46 +5528,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300171.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3.182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Full occupancy</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.537</v>
+      </c>
       <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3.18</v>
-      </c>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5665,6 +5634,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300159.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3.179</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>300171.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3.182</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5731,6 +5788,77 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>300237.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Full occupancy with atomic mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.727</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5812,77 +5940,6 @@
         <v>0.139</v>
       </c>
       <c r="C6" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Distance</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Atomic Mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>300237.cif</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Full occupancy with atomic mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
